--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487118_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487118_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5926</v>
+        <v>6.0013</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5649</v>
+        <v>7.4956</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0277</v>
+        <v>-1.4944</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.537</v>
+        <v>6.3637</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2964</v>
+        <v>0.1968</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2406</v>
+        <v>6.167</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7325</v>
+        <v>7.2385</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0745</v>
+        <v>2.1268</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.342</v>
+        <v>5.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2695</v>
+        <v>-0.8747</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3709</v>
+        <v>-1.93</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1014</v>
+        <v>1.0553</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>5.6732</v>
+        <v>0.3487</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>0.2572</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8732</v>
+        <v>0.0915</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4214</v>
+        <v>-2.0622</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9275</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5061</v>
+        <v>-2.0622</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>A. MASSALEY JR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1139</v>
+        <v>4.6914</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1169</v>
+        <v>3.9731</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.003</v>
+        <v>0.7184</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3637</v>
+        <v>3.0055</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1968</v>
+        <v>0.4886</v>
       </c>
       <c r="I3" t="n">
-        <v>6.167</v>
+        <v>2.5169</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2385</v>
+        <v>4.4342</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1268</v>
+        <v>2.432</v>
       </c>
       <c r="L3" t="n">
-        <v>5.1117</v>
+        <v>2.0021</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8747</v>
+        <v>-1.4287</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.93</v>
+        <v>-1.9435</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0553</v>
+        <v>0.5148</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5387</v>
+        <v>0.3417</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1216</v>
+        <v>-0.0026</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4171</v>
+        <v>0.3443</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.0622</v>
+        <v>1.5372</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0622</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MASSALEY JR</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4442</v>
+        <v>4.4962</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9935</v>
+        <v>3.9408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4507</v>
+        <v>0.5554</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0055</v>
+        <v>-0.537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4886</v>
+        <v>-0.2964</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5169</v>
+        <v>-0.2406</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4342</v>
+        <v>1.7325</v>
       </c>
       <c r="K4" t="n">
-        <v>2.432</v>
+        <v>2.0745</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0021</v>
+        <v>-0.342</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4287</v>
+        <v>-2.2695</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9435</v>
+        <v>-2.3709</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5148</v>
+        <v>0.1014</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9056</v>
+        <v>2.5768</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9822</v>
+        <v>1.1759</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0766</v>
+        <v>1.4009</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5372</v>
+        <v>3.4214</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4716</v>
+        <v>3.9275</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.5061</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. DARAME PIZARRO</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1096</v>
+        <v>3.1908</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0361</v>
+        <v>1.3719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0735</v>
+        <v>1.8189</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7304</v>
+        <v>1.6053</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0187</v>
+        <v>0.4172</v>
       </c>
       <c r="I5" t="n">
-        <v>0.749</v>
+        <v>1.1881</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6645</v>
+        <v>2.1261</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3621</v>
+        <v>1.4592</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3024</v>
+        <v>0.6669</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9341</v>
+        <v>-0.5208</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3808</v>
+        <v>-1.042</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5534</v>
+        <v>0.5212</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>-0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5143</v>
+        <v>1.199</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7998</v>
+        <v>0.276</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7145</v>
+        <v>0.923</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2859</v>
+        <v>0.9655</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5717</v>
+        <v>0.8999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>G. DARAME PIZARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9356</v>
+        <v>2.475</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4111</v>
+        <v>2.5354</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5245</v>
+        <v>-0.0603</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6053</v>
+        <v>0.7304</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4172</v>
+        <v>-0.0187</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1881</v>
+        <v>0.749</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1261</v>
+        <v>1.6645</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4592</v>
+        <v>0.3621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6669</v>
+        <v>1.3024</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5208</v>
+        <v>-0.9341</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.042</v>
+        <v>-0.3808</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5212</v>
+        <v>-0.5534</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.579</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0562</v>
+        <v>0.8798</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6848</v>
+        <v>0.2991</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6286</v>
+        <v>0.5807</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9655</v>
+        <v>0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8999</v>
+        <v>0.5717</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0912</v>
+        <v>-0.7931</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5985</v>
+        <v>0.0694</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5073</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9883</v>
+        <v>-0.383</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.2075</v>
+        <v>-0.3373</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2192</v>
+        <v>-0.0457</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7544</v>
+        <v>0.0707</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1789</v>
+        <v>0.1035</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4245</v>
+        <v>-0.0328</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2339</v>
+        <v>-0.4537</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0286</v>
+        <v>-0.4408</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7947</v>
+        <v>-0.0129</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2638</v>
+        <v>0.2968</v>
       </c>
       <c r="T7" t="n">
-        <v>1.051</v>
+        <v>-0.0013</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2128</v>
+        <v>0.2981</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3704</v>
+        <v>-0.8999</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3704</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4613</v>
+        <v>-1.2703</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3312</v>
+        <v>-2.1627</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1301</v>
+        <v>0.8924</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.383</v>
+        <v>-1.4428</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3373</v>
+        <v>-0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0457</v>
+        <v>-1.4066</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0707</v>
+        <v>-1.1296</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1035</v>
+        <v>0.1242</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0328</v>
+        <v>-1.2538</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4537</v>
+        <v>-0.3132</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4408</v>
+        <v>-0.1604</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0129</v>
+        <v>-0.1528</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3715</v>
+        <v>0.2304</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4019</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0304</v>
+        <v>0.2984</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8999</v>
+        <v>0.3281</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8999</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6164</v>
+        <v>-1.7317</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.482</v>
+        <v>-3.3996</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8656</v>
+        <v>1.6679</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4428</v>
+        <v>-0.9883</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0362</v>
+        <v>-3.2075</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4066</v>
+        <v>2.2192</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1296</v>
+        <v>-0.7544</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1242</v>
+        <v>-2.1789</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2538</v>
+        <v>1.4245</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3132</v>
+        <v>-0.2339</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1604</v>
+        <v>-1.0286</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1528</v>
+        <v>0.7947</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.386</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R9" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1157</v>
+        <v>0.6233</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3873</v>
+        <v>0.2499</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2716</v>
+        <v>0.3734</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3281</v>
+        <v>0.3704</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3281</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0294</v>
+        <v>-3.8569</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9243</v>
+        <v>-2.5644</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1051</v>
+        <v>-1.2925</v>
       </c>
       <c r="G10" t="n">
         <v>-2.684</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5889</v>
+        <v>0.7615</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2234</v>
+        <v>0.1365</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8123</v>
+        <v>0.6249</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1623</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2298</v>
+        <v>-5.5427</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2561</v>
+        <v>-3.8367</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9737</v>
+        <v>-1.706</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0372</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2625</v>
+        <v>-0.5754</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7588</v>
+        <v>-0.3394</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5037</v>
+        <v>-0.236</v>
       </c>
       <c r="V11" t="n">
         <v>-0.614</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.767800000000002</v>
+        <v>7.66</v>
       </c>
       <c r="E12" t="n">
-        <v>6.530399999999997</v>
+        <v>7.422799999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0.2374000000000001</v>
@@ -1357,7 +1357,7 @@
         <v>3.6326</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.177700000000001</v>
+        <v>-7.1777</v>
       </c>
       <c r="I12" t="n">
         <v>10.8103</v>
@@ -1366,10 +1366,10 @@
         <v>13.0445</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7438</v>
+        <v>4.743799999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>8.300700000000001</v>
+        <v>8.300699999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-9.4117</v>
@@ -1390,22 +1390,22 @@
         <v>9.650400000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>5.789999999999998</v>
+        <v>6.682600000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0908</v>
+        <v>1.9832</v>
       </c>
       <c r="U12" t="n">
-        <v>4.699199999999999</v>
+        <v>4.6992</v>
       </c>
       <c r="V12" t="n">
         <v>2.170100000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>6.8707</v>
+        <v>6.870699999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.7007</v>
+        <v>-4.700699999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7574</v>
+        <v>5.1267</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9257</v>
+        <v>5.724</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1683</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>5.6203</v>
@@ -1468,13 +1468,13 @@
         <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6458</v>
+        <v>0.0152</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8263</v>
+        <v>-0.3754</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8196</v>
+        <v>0.3906</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6405999999999999</v>
+        <v>1.4956</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3892</v>
+        <v>2.7898</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7486</v>
+        <v>-1.2942</v>
       </c>
       <c r="G14" t="n">
         <v>2.1599</v>
@@ -1546,13 +1546,13 @@
         <v>0.579</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4191</v>
+        <v>-0.5642</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8923</v>
+        <v>-0.4918</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5268</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.2859</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.321</v>
+        <v>0.7533</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6292</v>
+        <v>0.1402</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.613</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5206</v>
+        <v>0.2434</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4201</v>
+        <v>-1.3081</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9407</v>
+        <v>1.5516</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4211</v>
+        <v>1.5374</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1216</v>
+        <v>-0.9938</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7004</v>
+        <v>2.5312</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9418</v>
+        <v>-1.294</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7015</v>
+        <v>-0.3144</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2403</v>
+        <v>-0.9797</v>
       </c>
       <c r="P15" t="n">
-        <v>0.772</v>
+        <v>2.7021</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2346</v>
+        <v>-1.1696</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.078</v>
+        <v>-1.0691</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3126</v>
+        <v>-0.1005</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.165</v>
+        <v>-1.0226</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0422</v>
+        <v>-0.3281</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1228</v>
+        <v>-0.6945</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1762</v>
+        <v>0.1894</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1882</v>
+        <v>-0.3885</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3644</v>
+        <v>0.5779</v>
       </c>
       <c r="G16" t="n">
         <v>-0.026</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2023</v>
+        <v>0.2155</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1917</v>
+        <v>-0.0086</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0106</v>
+        <v>0.2241</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7501</v>
+        <v>-0.3407</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5608</v>
+        <v>-1.1299</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1894</v>
+        <v>0.7892</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2434</v>
+        <v>-0.5206</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3081</v>
+        <v>1.4201</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5516</v>
+        <v>-1.9407</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5374</v>
+        <v>1.4211</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9938</v>
+        <v>2.1216</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5312</v>
+        <v>-0.7004</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.294</v>
+        <v>-1.9418</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3144</v>
+        <v>-0.7015</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9797</v>
+        <v>-1.2403</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7021</v>
+        <v>0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
         <v>2.7021</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.673</v>
+        <v>-0.427</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.7701</v>
+        <v>-0.5787</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9029</v>
+        <v>0.1517</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0226</v>
+        <v>-0.165</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3281</v>
+        <v>-0.0422</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6945</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2122</v>
+        <v>-1.5515</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9535</v>
+        <v>-1.4528</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2587</v>
+        <v>-0.0988</v>
       </c>
       <c r="G19" t="n">
         <v>-4.426</v>
@@ -1936,13 +1936,13 @@
         <v>2.5091</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3775</v>
+        <v>-0.7168</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3537</v>
+        <v>-0.853</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0238</v>
+        <v>0.1361</v>
       </c>
       <c r="V19" t="n">
         <v>2.0473</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4149</v>
+        <v>-2.747</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1299</v>
+        <v>-1.7293</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.285</v>
+        <v>-1.0176</v>
       </c>
       <c r="G20" t="n">
         <v>0.3638</v>
@@ -2014,13 +2014,13 @@
         <v>0.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1574</v>
+        <v>-0.4895</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5949</v>
+        <v>-0.1943</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5625</v>
+        <v>-0.2952</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2702</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9874</v>
+        <v>-3.7102</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8594</v>
+        <v>-2.3316</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1281</v>
+        <v>-1.3787</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6668</v>
+        <v>-4.1736</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5455</v>
+        <v>1.4614</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1214</v>
+        <v>-5.635</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.7718</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0155</v>
+        <v>1.542</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6269</v>
+        <v>-3.3137</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0554</v>
+        <v>-2.4018</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5609</v>
+        <v>-0.0805</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4944</v>
+        <v>-2.3213</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.386</v>
+        <v>2.3161</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.579</v>
+        <v>2.3161</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3629</v>
+        <v>-0.502</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>-0.8457</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08</v>
+        <v>0.3437</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5717</v>
+        <v>-1.3508</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5717</v>
+        <v>-1.6366</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0913</v>
+        <v>-3.7736</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2314</v>
+        <v>-1.8594</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8599</v>
+        <v>-1.9142</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1736</v>
+        <v>-2.6668</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4614</v>
+        <v>-0.5455</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.635</v>
+        <v>-2.1214</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7718</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.542</v>
+        <v>0.0155</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.3137</v>
+        <v>-0.6269</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4018</v>
+        <v>-2.0554</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0805</v>
+        <v>-0.5609</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.3213</v>
+        <v>-1.4944</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3161</v>
+        <v>-0.386</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3161</v>
+        <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8831</v>
+        <v>-0.149</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7456</v>
+        <v>-0.2829</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1375</v>
+        <v>0.1338</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3508</v>
+        <v>-0.5717</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6366</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="23">
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7677</v>
+        <v>-4.765000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2374999999999989</v>
+        <v>-0.2375000000000007</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.5305</v>
+        <v>-4.5277</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.632599999999999</v>
+        <v>-3.6326</v>
       </c>
       <c r="H23" t="n">
         <v>7.1776</v>
@@ -2233,13 +2233,13 @@
         <v>-13.0443</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.743799999999999</v>
+        <v>-4.7438</v>
       </c>
       <c r="O23" t="n">
         <v>-8.300699999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>4.825200000000001</v>
+        <v>4.8252</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.6503</v>
@@ -2248,13 +2248,13 @@
         <v>14.4755</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.7903</v>
+        <v>-3.7874</v>
       </c>
       <c r="T23" t="n">
         <v>-4.6995</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0907</v>
+        <v>0.9119</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1699</v>
